--- a/output/diff_report.xlsx
+++ b/output/diff_report.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,15 +48,11 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00991B1B"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <color rgb="0092400E"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -86,11 +82,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -125,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -142,13 +133,10 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -539,7 +527,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-01 10:57:13</t>
+          <t>2026-06-08 10:44:33</t>
         </is>
       </c>
     </row>
@@ -551,7 +539,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>powerBi\v3</t>
+          <t>powerBi\v1</t>
         </is>
       </c>
     </row>
@@ -563,7 +551,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>powerBi\v4</t>
+          <t>powerBi\v2</t>
         </is>
       </c>
     </row>
@@ -596,7 +584,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -611,7 +599,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -671,7 +659,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -701,7 +689,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -745,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -792,7 +780,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Product Detail</t>
+          <t>LocalDateTable_370c322f-a9fe-49ca-9c41-7f796dcf9369</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -802,107 +790,84 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Date, Year = YEAR([Date]), MonthNo = MONTH([Date]), Month = FORMAT([Date], "MMMM"), QuarterNo = INT(([MonthNo] + 2) / 3), Quarter = "Qtr " &amp; [QuarterNo], Day = DAY([Date])</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>LocalDateTable_53a5f2dc-55d7-429e-b6a8-356c169d4812</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Date, Year = YEAR([Date]), MonthNo = MONTH([Date]), Month = FORMAT([Date], "MMMM"), QuarterNo = INT(([MonthNo] + 2) / 3), Quarter = "Qtr " &amp; [QuarterNo], Day = DAY([Date])</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>LocalDateTable_8b371d35-fee7-4c0c-88e3-6e669f04fb7f</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Date, Year = YEAR([Date]), MonthNo = MONTH([Date]), Month = FORMAT([Date], "MMMM"), QuarterNo = INT(([MonthNo] + 2) / 3), Quarter = "Qtr " &amp; [QuarterNo], Day = DAY([Date])</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>PowerBI-Datasets-main</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Product Key, ProductSubcategoryKey, ProductSKU, ProductName, Product Code, ProductDescription, Product Units, Product Style, ProductCost, ProductPrice</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>LocalDateTable_370c322f-a9fe-49ca-9c41-7f796dcf9369</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Removed</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Date, Year = YEAR([Date]), MonthNo = MONTH([Date]), Month = FORMAT([Date], "MMMM"), QuarterNo = INT(([MonthNo] + 2) / 3), Quarter = "Qtr " &amp; [QuarterNo], Day = DAY([Date])</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>LocalDateTable_53a5f2dc-55d7-429e-b6a8-356c169d4812</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Removed</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Date, Year = YEAR([Date]), MonthNo = MONTH([Date]), Month = FORMAT([Date], "MMMM"), QuarterNo = INT(([MonthNo] + 2) / 3), Quarter = "Qtr " &amp; [QuarterNo], Day = DAY([Date])</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>LocalDateTable_8b371d35-fee7-4c0c-88e3-6e669f04fb7f</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Removed</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Date, Year = YEAR([Date]), MonthNo = MONTH([Date]), Month = FORMAT([Date], "MMMM"), QuarterNo = INT(([MonthNo] + 2) / 3), Quarter = "Qtr " &amp; [QuarterNo], Day = DAY([Date])</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>PowerBI-Datasets-main</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Removed</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Name, Extension, Date accessed, Date modified, Date created, Folder Path, Column</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Name, Extension, Date accessed, Date modified, Date created, Folder Path</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -970,7 +935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1004,12 +969,12 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Old DAX</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>New DAX</t>
         </is>
@@ -1019,6 +984,126 @@
           <t>Format String</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Customers1</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Customers1.AvgAge</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>AVERAGE( Customers1[Age] )</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Customers1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Customers1.AvgAnnualIncome</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>AVERAGE( Customers1[AnnualIncome] )</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Customers1</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Customers1.CustomerCount</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>DISTINCTCOUNT( Customers1[CustomerID] )</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Customers1</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Customers1.TotalAnnualIncome</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>SUM( Customers1[AnnualIncome] )</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Customers1</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Customers1.TotalChildren_Sum</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>SUM( Customers1[TotalChildren] )</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1092,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1161,66 +1246,253 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>79fd993ca34ce06828c4</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>tableEx</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>8bfdbd317dd58e392a95</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>clusteredBarChart</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>clusteredColumnChart</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>clusteredBarChart</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>83a29ad0eb9c2b78de89</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>pieChart</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Auto Charts</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Page Added</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>1_bar_gender_annualincome</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>clusteredBarChart</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>New Visual</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Customers1.Gender, Sum(Customers1.AnnualIncome)</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Auto Charts</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Page Added</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>2_pie_education_income</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>donutChart</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>New Visual</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Customers1.EducationLevel, Sum(Customers1.AnnualIncome)</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Auto Charts</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Page Added</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>3_column_occupation_income</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>clusteredColumnChart</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>New Visual</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Customers1.Occupation, Sum(Customers1.AnnualIncome)</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Auto Charts</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Page Added</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>4_scatter_age_income</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>scatterChart</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>New Visual</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Customers1.Age, Sum(Customers1.AnnualIncome)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Auto Charts</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Page Added</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>5_card_avg_income</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>card</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>New Visual</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Avg(Customers1.AnnualIncome)</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Auto Charts</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Page Added</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>6_stacked_marital_income</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>stackedColumnChart</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>New Visual</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Customers1.MaritalStatus, Sum(Customers1.AnnualIncome)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
